--- a/feedback_forms/017_skincare_product_refill_program_interest_survey--feedback_forms.xlsx
+++ b/feedback_forms/017_skincare_product_refill_program_interest_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Somewhat satisfied</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>program_satisfaction_choices</t>
+          <t>demographics_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Online Search</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Online Search</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>friend/family</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Friend/Family</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>friend/family</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Friend/Family</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>in-store_display</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>In-store Display</t>
         </is>
       </c>
     </row>
@@ -2168,29 +2168,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>in-store_display</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>In-store Display</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>demographics_2_choices</t>
+          <t>product_loyalty_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>every_1-2_weeks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Every 1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>every_1-2_weeks</t>
+          <t>every_3-4_weeks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Every 1-2 weeks</t>
+          <t>Every 3-4 weeks</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>every_3-4_weeks</t>
+          <t>every_4-6_weeks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Every 3-4 weeks</t>
+          <t>Every 4-6 weeks</t>
         </is>
       </c>
     </row>
@@ -2236,29 +2236,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>every_4-6_weeks</t>
+          <t>every_2_months</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Every 4-6 weeks</t>
+          <t>Every 2 months</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>product_loyalty_choices</t>
+          <t>product_loyalty_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>every_2_months</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Every 2 months</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Not likely</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Somewhat likely</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2304,80 +2304,80 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>product_loyalty_2_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Somewhat likely</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>product_loyalty_2_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Very likely</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>survey_completion_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>for_fun</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>For fun</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>survey_completion_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>to_provide_feedback</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>To provide feedback</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>for_fun</t>
+          <t>to_provide_information_about_our_skincare_product_refill_program</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>For fun</t>
+          <t>To provide information about our Skincare Product Refill Program</t>
         </is>
       </c>
     </row>
@@ -2406,44 +2406,10 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>to_provide_feedback</t>
+          <t>to_participate_in_a_contest</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
-        <is>
-          <t>To provide feedback</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>survey_completion_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>to_provide_information_about_our_skincare_product_refill_program</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>To provide information about our Skincare Product Refill Program</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>survey_completion_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>to_participate_in_a_contest</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
         <is>
           <t>To participate in a contest</t>
         </is>
